--- a/sim/resources/sample/VisitorLevel.xlsx
+++ b/sim/resources/sample/VisitorLevel.xlsx
@@ -55,12 +55,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+概率_道具ID_数量</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
@@ -83,12 +105,18 @@
     <t>固定产出</t>
   </si>
   <si>
+    <t>额外材料掉落</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>Map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
+    <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -104,19 +132,37 @@
     <t>Reward</t>
   </si>
   <si>
+    <t>BonusRate</t>
+  </si>
+  <si>
     <t>普通路人1</t>
   </si>
   <si>
     <t>1990000_10000</t>
   </si>
   <si>
+    <t>0_1980000_20000</t>
+  </si>
+  <si>
     <t>1990000_11000</t>
   </si>
   <si>
+    <t>5_1980000_20000</t>
+  </si>
+  <si>
     <t>普通路人2</t>
   </si>
   <si>
+    <t>8_1980000_20000</t>
+  </si>
+  <si>
+    <t>10_1980000_20000</t>
+  </si>
+  <si>
     <t>普通路人3</t>
+  </si>
+  <si>
+    <t>15_1980000_20000</t>
   </si>
   <si>
     <t>精英白领1</t>
@@ -189,7 +235,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +251,12 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -723,137 +775,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -870,12 +922,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -887,10 +942,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1209,18 +1267,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G86"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="4" width="11.75" customWidth="1"/>
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="14.75" customWidth="1"/>
-    <col min="7" max="7" width="40.5" customWidth="1"/>
+    <col min="7" max="7" width="29.875" customWidth="1"/>
+    <col min="8" max="8" width="31.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1242,728 +1301,959 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" spans="1:7">
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" spans="1:7">
+      <c r="F2" s="6"/>
+      <c r="G2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" spans="1:7">
+      <c r="E3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" spans="1:8">
       <c r="A4" s="1"/>
-      <c r="B4" s="7"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:7">
+      <c r="E4" s="8"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:8">
       <c r="A5" s="1">
         <f>B5*1000+C5</f>
-        <v>101001</v>
+        <v>1001001</v>
       </c>
       <c r="B5" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="F5" s="9"/>
+      <c r="G5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A34" si="0">B6*1000+C6</f>
-        <v>101002</v>
+        <v>1001002</v>
       </c>
       <c r="B6" s="1">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="C6" s="2">
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="F6" s="9"/>
+      <c r="G6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>102001</v>
+        <v>1002001</v>
       </c>
       <c r="B7" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="F7" s="9"/>
+      <c r="G7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>102002</v>
+        <v>1002002</v>
       </c>
       <c r="B8" s="1">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1">
         <v>10</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="F8" s="9"/>
+      <c r="G8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>103001</v>
+        <v>1003001</v>
       </c>
       <c r="B9" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="F9" s="9"/>
+      <c r="G9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>103002</v>
+        <v>1003002</v>
       </c>
       <c r="B10" s="1">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="F10" s="9"/>
+      <c r="G10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>201001</v>
+        <v>2001001</v>
       </c>
       <c r="B11" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="F11" s="9"/>
+      <c r="G11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>201002</v>
+        <v>2001002</v>
       </c>
       <c r="B12" s="1">
-        <v>201</v>
+        <v>2001</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1">
         <v>10</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="F12" s="9"/>
+      <c r="G12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>202001</v>
+        <v>2002001</v>
       </c>
       <c r="B13" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="F13" s="9"/>
+      <c r="G13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>202002</v>
+        <v>2002002</v>
       </c>
       <c r="B14" s="1">
-        <v>202</v>
+        <v>2002</v>
       </c>
       <c r="C14" s="2">
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1">
         <v>10</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="F14" s="9"/>
+      <c r="G14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>203001</v>
+        <v>2003001</v>
       </c>
       <c r="B15" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="F15" s="9"/>
+      <c r="G15" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>203002</v>
+        <v>2003002</v>
       </c>
       <c r="B16" s="1">
-        <v>203</v>
+        <v>2003</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E16" s="1">
         <v>10</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="10" t="s">
+      <c r="F16" s="9"/>
+      <c r="G16" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>301001</v>
+        <v>3001001</v>
       </c>
       <c r="B17" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="F17" s="9"/>
+      <c r="G17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>301002</v>
+        <v>3001002</v>
       </c>
       <c r="B18" s="1">
-        <v>301</v>
+        <v>3001</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E18" s="1">
         <v>10</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="F18" s="9"/>
+      <c r="G18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>302001</v>
+        <v>3002001</v>
       </c>
       <c r="B19" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="F19" s="9"/>
+      <c r="G19" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>302002</v>
+        <v>3002002</v>
       </c>
       <c r="B20" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E20" s="1">
         <v>10</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="F20" s="9"/>
+      <c r="G20" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>303001</v>
+        <v>3003001</v>
       </c>
       <c r="B21" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="F21" s="9"/>
+      <c r="G21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>303002</v>
+        <v>3003002</v>
       </c>
       <c r="B22" s="1">
-        <v>303</v>
+        <v>3003</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E22" s="1">
         <v>10</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="F22" s="9"/>
+      <c r="G22" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>401001</v>
+        <v>4001001</v>
       </c>
       <c r="B23" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="F23" s="9"/>
+      <c r="G23" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>401002</v>
+        <v>4001002</v>
       </c>
       <c r="B24" s="1">
-        <v>401</v>
+        <v>4001</v>
       </c>
       <c r="C24" s="2">
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E24" s="1">
         <v>10</v>
       </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="F24" s="9"/>
+      <c r="G24" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>402001</v>
+        <v>4002001</v>
       </c>
       <c r="B25" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="F25" s="9"/>
+      <c r="G25" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>402002</v>
+        <v>4002002</v>
       </c>
       <c r="B26" s="1">
-        <v>402</v>
+        <v>4002</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E26" s="1">
         <v>10</v>
       </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="F26" s="9"/>
+      <c r="G26" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>403001</v>
+        <v>4003001</v>
       </c>
       <c r="B27" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="F27" s="9"/>
+      <c r="G27" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>403002</v>
+        <v>4003002</v>
       </c>
       <c r="B28" s="1">
-        <v>403</v>
+        <v>4003</v>
       </c>
       <c r="C28" s="2">
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E28" s="1">
         <v>10</v>
       </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="F28" s="9"/>
+      <c r="G28" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>501001</v>
+        <v>5001001</v>
       </c>
       <c r="B29" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="F29" s="9"/>
+      <c r="G29" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>501002</v>
+        <v>5001002</v>
       </c>
       <c r="B30" s="1">
-        <v>501</v>
+        <v>5001</v>
       </c>
       <c r="C30" s="2">
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E30" s="1">
         <v>10</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="F30" s="9"/>
+      <c r="G30" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>502001</v>
+        <v>5002001</v>
       </c>
       <c r="B31" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="F31" s="9"/>
+      <c r="G31" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
-        <v>502002</v>
+        <v>5002002</v>
       </c>
       <c r="B32" s="1">
-        <v>502</v>
+        <v>5002</v>
       </c>
       <c r="C32" s="2">
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E32" s="1">
         <v>10</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="F32" s="9"/>
+      <c r="G32" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
-        <v>503001</v>
+        <v>5003001</v>
       </c>
       <c r="B33" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E33" s="1">
         <v>0</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="F33" s="9"/>
+      <c r="G33" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
-        <v>503002</v>
+        <v>5003002</v>
       </c>
       <c r="B34" s="1">
-        <v>503</v>
+        <v>5003</v>
       </c>
       <c r="C34" s="2">
         <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E34" s="1">
         <v>10</v>
       </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" ht="17.25" spans="4:5">
-      <c r="D68" s="11"/>
-    </row>
-    <row r="69" ht="14.25" spans="4:5">
-      <c r="E69" s="12"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="H47" s="12"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="H48" s="12"/>
+    </row>
+    <row r="49" spans="8:8">
+      <c r="H49" s="12"/>
+    </row>
+    <row r="50" spans="8:8">
+      <c r="H50" s="12"/>
+    </row>
+    <row r="51" spans="8:8">
+      <c r="H51" s="12"/>
+    </row>
+    <row r="52" spans="8:8">
+      <c r="H52" s="12"/>
+    </row>
+    <row r="53" spans="8:8">
+      <c r="H53" s="12"/>
+    </row>
+    <row r="54" spans="8:8">
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" spans="8:8">
+      <c r="H55" s="12"/>
+    </row>
+    <row r="56" spans="8:8">
+      <c r="H56" s="12"/>
+    </row>
+    <row r="57" spans="8:8">
+      <c r="H57" s="12"/>
+    </row>
+    <row r="58" spans="8:8">
+      <c r="H58" s="12"/>
+    </row>
+    <row r="59" spans="8:8">
+      <c r="H59" s="12"/>
+    </row>
+    <row r="60" spans="8:8">
+      <c r="H60" s="12"/>
+    </row>
+    <row r="61" spans="8:8">
+      <c r="H61" s="12"/>
+    </row>
+    <row r="62" spans="8:8">
+      <c r="H62" s="12"/>
+    </row>
+    <row r="63" spans="8:8">
+      <c r="H63" s="12"/>
+    </row>
+    <row r="64" spans="8:8">
+      <c r="H64" s="12"/>
+    </row>
+    <row r="65" spans="4:8">
+      <c r="H65" s="12"/>
+    </row>
+    <row r="66" spans="4:8">
+      <c r="H66" s="12"/>
+    </row>
+    <row r="67" spans="4:8">
+      <c r="H67" s="12"/>
+    </row>
+    <row r="68" ht="17.25" spans="4:8">
+      <c r="D68" s="13"/>
+      <c r="H68" s="12"/>
+    </row>
+    <row r="69" ht="14.25" spans="4:8">
+      <c r="E69" s="14"/>
+      <c r="H69" s="12"/>
+    </row>
+    <row r="70" spans="4:8">
+      <c r="H70" s="12"/>
+    </row>
+    <row r="71" spans="4:8">
+      <c r="H71" s="12"/>
+    </row>
+    <row r="72" spans="4:8">
+      <c r="H72" s="12"/>
+    </row>
+    <row r="73" spans="4:8">
+      <c r="H73" s="12"/>
+    </row>
+    <row r="74" spans="4:8">
+      <c r="H74" s="12"/>
+    </row>
+    <row r="75" spans="4:8">
+      <c r="H75" s="12"/>
+    </row>
+    <row r="76" spans="4:8">
+      <c r="H76" s="12"/>
+    </row>
+    <row r="77" spans="4:8">
+      <c r="H77" s="12"/>
+    </row>
+    <row r="78" spans="4:8">
+      <c r="H78" s="12"/>
+    </row>
+    <row r="79" spans="4:8">
+      <c r="H79" s="12"/>
     </row>
     <row r="82" ht="14.25" spans="4:5">
-      <c r="D82" s="12"/>
+      <c r="D82" s="14"/>
     </row>
     <row r="85" ht="14.25" spans="4:5">
-      <c r="E85" s="12"/>
+      <c r="E85" s="14"/>
     </row>
     <row r="86" ht="14.25" spans="4:5">
-      <c r="E86" s="12"/>
+      <c r="E86" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
